--- a/output/pdf_financials_xlsx/TOU.xlsx
+++ b/output/pdf_financials_xlsx/TOU.xlsx
@@ -938,43 +938,43 @@
         <v>271.49</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0</v>
+        <v>381.478</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0</v>
+        <v>494.103</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0</v>
+        <v>580.884</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0</v>
+        <v>1072.877</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0</v>
+        <v>1080.115</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0</v>
+        <v>1368.426</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0</v>
+        <v>1480.162</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0</v>
+        <v>1713.847</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0</v>
+        <v>1697.597</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0</v>
+        <v>2873.572</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>0</v>
+        <v>3293.188</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>0</v>
+        <v>3592.157</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>0</v>
+        <v>5564.679</v>
       </c>
     </row>
     <row r="11">
@@ -7496,19 +7496,19 @@
         <v>0</v>
       </c>
       <c r="M124" s="3" t="n">
-        <v>0</v>
+        <v>-4.081</v>
       </c>
       <c r="N124" s="3" t="n">
-        <v>0</v>
+        <v>-3.692</v>
       </c>
       <c r="O124" s="3" t="n">
-        <v>0</v>
+        <v>-5.743</v>
       </c>
       <c r="P124" s="3" t="n">
-        <v>0</v>
+        <v>-9.192</v>
       </c>
       <c r="Q124" s="3" t="n">
-        <v>0</v>
+        <v>-11.778</v>
       </c>
     </row>
     <row r="125">
@@ -7555,19 +7555,19 @@
         <v>0</v>
       </c>
       <c r="M125" s="3" t="n">
-        <v>0</v>
+        <v>-4.081</v>
       </c>
       <c r="N125" s="3" t="n">
-        <v>0</v>
+        <v>-3.692</v>
       </c>
       <c r="O125" s="3" t="n">
-        <v>0</v>
+        <v>-5.743</v>
       </c>
       <c r="P125" s="3" t="n">
-        <v>0</v>
+        <v>-9.192</v>
       </c>
       <c r="Q125" s="3" t="n">
-        <v>0</v>
+        <v>-11.778</v>
       </c>
     </row>
     <row r="126">
@@ -32550,7 +32550,11 @@
           <t>Lease payments (note 8)</t>
         </is>
       </c>
-      <c r="D257" t="inlineStr"/>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E257" t="inlineStr">
         <is>
           <t>-</t>
@@ -34226,7 +34230,11 @@
           <t>Lease payments (note 7)</t>
         </is>
       </c>
-      <c r="D275" t="inlineStr"/>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E275" t="inlineStr">
         <is>
           <t>-</t>
@@ -37112,7 +37120,11 @@
           <t>Lease payments (note 7)</t>
         </is>
       </c>
-      <c r="D306" t="inlineStr"/>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E306" t="inlineStr">
         <is>
           <t>-</t>
@@ -47994,7 +48006,7 @@
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E425" t="inlineStr">
@@ -55160,7 +55172,7 @@
       </c>
       <c r="D504" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E504" t="inlineStr">
@@ -56934,7 +56946,7 @@
       </c>
       <c r="D523" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E523" t="inlineStr">
@@ -60340,7 +60352,7 @@
       </c>
       <c r="D559" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E559" s="5" t="n">

--- a/output/pdf_financials_xlsx/TOU.xlsx
+++ b/output/pdf_financials_xlsx/TOU.xlsx
@@ -1335,7 +1335,7 @@
         <v>-81.863</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>-0</v>
+        <v>4.05</v>
       </c>
       <c r="J17" s="3" t="n">
         <v>-152.06</v>
@@ -1563,10 +1563,8 @@
       <c r="H20" s="3" t="n">
         <v>80.087</v>
       </c>
-      <c r="I20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I20" s="3" t="n">
+        <v>-31.971</v>
       </c>
       <c r="J20" s="3" t="n">
         <v>346.773</v>
@@ -1733,7 +1731,7 @@
         <v>80.087</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>-36.021</v>
+        <v>-31.971</v>
       </c>
       <c r="J23" s="3" t="n">
         <v>346.773</v>
@@ -2265,7 +2263,7 @@
         <v>50.54831738190799</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>-0</v>
+        <v>-11.24344132589323</v>
       </c>
       <c r="J31" s="3" t="n">
         <v>30.48314766665397</v>
@@ -4440,13 +4438,13 @@
         <v>0</v>
       </c>
       <c r="O70" s="3" t="n">
-        <v>0</v>
+        <v>5.796</v>
       </c>
       <c r="P70" s="3" t="n">
-        <v>0</v>
+        <v>8.385</v>
       </c>
       <c r="Q70" s="3" t="n">
-        <v>0</v>
+        <v>8.034000000000001</v>
       </c>
     </row>
     <row r="71">
@@ -4495,13 +4493,13 @@
         <v>0</v>
       </c>
       <c r="O71" s="3" t="n">
-        <v>0</v>
+        <v>5.796</v>
       </c>
       <c r="P71" s="3" t="n">
-        <v>0</v>
+        <v>8.385</v>
       </c>
       <c r="Q71" s="3" t="n">
-        <v>800</v>
+        <v>808.034</v>
       </c>
     </row>
     <row r="72">
@@ -4715,13 +4713,13 @@
         <v>1435.608</v>
       </c>
       <c r="O75" s="3" t="n">
-        <v>492.391</v>
+        <v>486.595</v>
       </c>
       <c r="P75" s="3" t="n">
-        <v>190.759</v>
+        <v>182.374</v>
       </c>
       <c r="Q75" s="3" t="n">
-        <v>234.224</v>
+        <v>226.19</v>
       </c>
     </row>
     <row r="76">
@@ -5015,16 +5013,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O80" s="3" t="n">
+        <v>0.0004135347438749447</v>
       </c>
       <c r="P80" s="3" t="n">
-        <v>0.08188437349374957</v>
+        <v>0.08242382506354398</v>
       </c>
       <c r="Q80" s="3" t="n">
-        <v>0.1200363196361195</v>
+        <v>0.1205567818874472</v>
       </c>
     </row>
     <row r="81">
@@ -6009,7 +6005,7 @@
         <v>80.087</v>
       </c>
       <c r="I99" s="3" t="n">
-        <v>-36.021</v>
+        <v>-31.971</v>
       </c>
       <c r="J99" s="3" t="n">
         <v>346.773</v>
@@ -6393,56 +6389,52 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>0</v>
+        <v>-22.236</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0</v>
+        <v>10.078</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-12.931</v>
+      </c>
+      <c r="E106" s="3" t="n">
+        <v>-6.802</v>
+      </c>
+      <c r="F106" s="3" t="n">
+        <v>-47.522</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>0</v>
+        <v>-13.621</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>0</v>
+        <v>-14.465</v>
       </c>
       <c r="I106" s="3" t="n">
-        <v>0</v>
+        <v>-34.9</v>
       </c>
       <c r="J106" s="3" t="n">
-        <v>0</v>
+        <v>-22.858</v>
       </c>
       <c r="K106" s="3" t="n">
-        <v>0</v>
+        <v>-33.971</v>
       </c>
       <c r="L106" s="3" t="n">
-        <v>0</v>
+        <v>-30.611</v>
       </c>
       <c r="M106" s="3" t="n">
-        <v>0</v>
+        <v>-82.009</v>
       </c>
       <c r="N106" s="3" t="n">
-        <v>0</v>
+        <v>-203.152</v>
       </c>
       <c r="O106" s="3" t="n">
-        <v>0</v>
+        <v>307.659</v>
       </c>
       <c r="P106" s="3" t="n">
-        <v>0</v>
+        <v>-27.116</v>
       </c>
       <c r="Q106" s="3" t="n">
-        <v>0</v>
+        <v>-10.397</v>
       </c>
     </row>
     <row r="107">
@@ -6628,20 +6620,16 @@
         <v>0</v>
       </c>
       <c r="C110" s="3" t="n">
-        <v>0</v>
+        <v>1.128</v>
       </c>
       <c r="D110" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>1.315</v>
+      </c>
+      <c r="E110" s="3" t="n">
+        <v>1.328</v>
+      </c>
+      <c r="F110" s="3" t="n">
+        <v>2.038</v>
       </c>
       <c r="G110" s="3" t="n">
         <v>0</v>
@@ -6662,19 +6650,19 @@
         <v>0.848</v>
       </c>
       <c r="M110" s="3" t="n">
-        <v>0.985</v>
+        <v>12.842</v>
       </c>
       <c r="N110" s="3" t="n">
-        <v>0.985</v>
+        <v>22.138</v>
       </c>
       <c r="O110" s="3" t="n">
-        <v>0.681</v>
+        <v>20.043</v>
       </c>
       <c r="P110" s="3" t="n">
-        <v>2.062</v>
+        <v>29.971</v>
       </c>
       <c r="Q110" s="3" t="n">
-        <v>0</v>
+        <v>35.162</v>
       </c>
     </row>
     <row r="111">
@@ -6923,15 +6911,13 @@
         <v>0</v>
       </c>
       <c r="C115" s="3" t="n">
-        <v>0</v>
+        <v>0.255</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>3.588</v>
+      </c>
+      <c r="E115" s="3" t="n">
+        <v>0.168</v>
       </c>
       <c r="F115" s="1" t="inlineStr">
         <is>
@@ -6966,10 +6952,10 @@
         <v>0</v>
       </c>
       <c r="P115" s="3" t="n">
-        <v>0</v>
+        <v>331.465</v>
       </c>
       <c r="Q115" s="3" t="n">
-        <v>0</v>
+        <v>221.226</v>
       </c>
     </row>
     <row r="116">
@@ -9744,7 +9730,11 @@
           <t>Lease liabilities (note 8)</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>-</t>
@@ -11056,7 +11046,11 @@
           <t>Lease liabilities (note 7)</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
           <t>-</t>
@@ -31042,7 +31036,11 @@
           <t>Accretion (note 9)</t>
         </is>
       </c>
-      <c r="D240" t="inlineStr"/>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E240" t="inlineStr">
         <is>
           <t>-</t>
@@ -31398,7 +31396,11 @@
           <t>Deferred tax expense (note 14)</t>
         </is>
       </c>
-      <c r="D244" t="inlineStr"/>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E244" t="inlineStr">
         <is>
           <t>-</t>
@@ -32312,7 +32314,11 @@
           <t>Changes in non-cash operating working capital</t>
         </is>
       </c>
-      <c r="D254" t="inlineStr"/>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E254" s="5" t="n">
         <v>-22.236</v>
       </c>
@@ -33204,7 +33210,11 @@
           <t>Proceeds from sale of investments (note 11)</t>
         </is>
       </c>
-      <c r="D264" t="inlineStr"/>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E264" t="inlineStr">
         <is>
           <t>-</t>
@@ -33588,7 +33598,11 @@
           <t>Accretion (note 8)</t>
         </is>
       </c>
-      <c r="D268" t="inlineStr"/>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E268" t="inlineStr">
         <is>
           <t>-</t>
@@ -33862,7 +33876,11 @@
           <t>Deferred tax expense</t>
         </is>
       </c>
-      <c r="D271" t="inlineStr"/>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E271" t="inlineStr">
         <is>
           <t>-</t>
@@ -35518,7 +35536,11 @@
           <t>Changes in non-cash operating working capital (note 20)</t>
         </is>
       </c>
-      <c r="D289" t="inlineStr"/>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E289" t="inlineStr">
         <is>
           <t>-</t>
@@ -36176,7 +36198,11 @@
           <t>Deferred tax expense (note 14)</t>
         </is>
       </c>
-      <c r="D296" t="inlineStr"/>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E296" t="inlineStr">
         <is>
           <t>-</t>
@@ -36932,7 +36958,11 @@
           <t>Changes in non-cash operating working capital (note 20)</t>
         </is>
       </c>
-      <c r="D304" t="inlineStr"/>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E304" t="inlineStr">
         <is>
           <t>-</t>
@@ -38080,7 +38110,11 @@
           <t>Deferred taxes (recovery) (note 14)</t>
         </is>
       </c>
-      <c r="D316" t="inlineStr"/>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E316" t="inlineStr">
         <is>
           <t>-</t>
@@ -38742,7 +38776,11 @@
           <t>Changes in non-cash operating working capital (note 20)</t>
         </is>
       </c>
-      <c r="D323" t="inlineStr"/>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E323" t="inlineStr">
         <is>
           <t>-</t>
@@ -39832,7 +39870,11 @@
           <t>Changes in non-cash operating working capital (note 19)</t>
         </is>
       </c>
-      <c r="D335" t="inlineStr"/>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E335" t="inlineStr">
         <is>
           <t>-</t>
@@ -40612,7 +40654,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D344" t="inlineStr"/>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E344" s="5" t="n">
         <v>-2.121</v>
       </c>
@@ -40700,7 +40746,11 @@
           <t>Deferred taxes (recovery)</t>
         </is>
       </c>
-      <c r="D345" t="inlineStr"/>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E345" t="inlineStr">
         <is>
           <t>-</t>
@@ -40792,7 +40842,11 @@
           <t>Changes in non-cash operating working capital (note 18)</t>
         </is>
       </c>
-      <c r="D346" t="inlineStr"/>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E346" t="inlineStr">
         <is>
           <t>-</t>
@@ -41508,7 +41562,11 @@
           <t>Changes in non-cash operating working capital (note 18)</t>
         </is>
       </c>
-      <c r="D354" t="inlineStr"/>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E354" t="inlineStr">
         <is>
           <t>-</t>
@@ -42250,7 +42308,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D362" t="inlineStr"/>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E362" t="inlineStr">
         <is>
           <t>-</t>
@@ -42622,7 +42684,11 @@
           <t>Changes in non-cash operating working capital (note 18)</t>
         </is>
       </c>
-      <c r="D366" t="inlineStr"/>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E366" t="inlineStr">
         <is>
           <t>-</t>
@@ -43660,7 +43726,11 @@
           <t>Changes in non-cash operating working capital (note 18)</t>
         </is>
       </c>
-      <c r="D377" t="inlineStr"/>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E377" t="inlineStr">
         <is>
           <t>-</t>
@@ -43848,7 +43918,11 @@
           <t>Proceeds from sale of investments</t>
         </is>
       </c>
-      <c r="D379" t="inlineStr"/>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E379" t="inlineStr">
         <is>
           <t>-</t>
@@ -44506,7 +44580,11 @@
           <t>Changes in non-cash operating working capital (note 20)</t>
         </is>
       </c>
-      <c r="D386" t="inlineStr"/>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E386" t="inlineStr">
         <is>
           <t>-</t>
